--- a/Design/Example.xlsx
+++ b/Design/Example.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6785D761-BCD1-451D-A0A9-81ADA5CBF265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9698" yWindow="773" windowWidth="21600" windowHeight="11333" activeTab="2"/>
+    <workbookView xWindow="2213" yWindow="2685" windowWidth="25845" windowHeight="11783" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ledger" sheetId="1" r:id="rId1"/>
@@ -12,22 +13,11 @@
     <sheet name="Income" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
     <t>Date</t>
   </si>
@@ -62,12 +52,6 @@
     <t>6:00p</t>
   </si>
   <si>
-    <t>Go over questions for market survey</t>
-  </si>
-  <si>
-    <t>Research</t>
-  </si>
-  <si>
     <t>Excelsior</t>
   </si>
   <si>
@@ -77,18 +61,12 @@
     <t>Amount</t>
   </si>
   <si>
-    <t>Tax Year</t>
-  </si>
-  <si>
     <t>BT</t>
   </si>
   <si>
     <t>Menu</t>
   </si>
   <si>
-    <t>Paid</t>
-  </si>
-  <si>
     <t>Charlie Wonder, Zach Smith</t>
   </si>
   <si>
@@ -119,16 +97,16 @@
     <t>ABC, DEF</t>
   </si>
   <si>
-    <t>Bonus</t>
-  </si>
-  <si>
-    <t>X</t>
+    <t>Design main menu</t>
+  </si>
+  <si>
+    <t>Design</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
   </numFmts>
@@ -186,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -219,9 +197,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -242,9 +217,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -282,7 +257,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -354,7 +329,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -527,7 +502,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -549,7 +524,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -567,7 +542,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>6</v>
@@ -590,25 +565,25 @@
         <v>10</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>13</v>
-      </c>
       <c r="J2" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -618,7 +593,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -628,30 +603,30 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -660,22 +635,21 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.19921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.19921875" style="9" customWidth="1"/>
-    <col min="7" max="7" width="7.53125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.19921875" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -683,37 +657,19 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>16</v>
-      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B2" s="7">
-        <v>10000</v>
+        <v>150</v>
       </c>
       <c r="C2" s="9">
         <v>44927</v>
       </c>
       <c r="D2" s="9">
-        <v>45047</v>
-      </c>
-      <c r="E2" s="9">
-        <v>45078</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="5">
-        <v>2011</v>
+        <v>45291</v>
       </c>
     </row>
   </sheetData>
